--- a/build/filters/questions-2026-08-06/Questions-for-Branko-Cicovic_Filters-and-Schedule_Friendly-Version_2026-08-06.xlsx
+++ b/build/filters/questions-2026-08-06/Questions-for-Branko-Cicovic_Filters-and-Schedule_Friendly-Version_2026-08-06.xlsx
@@ -860,9 +860,10 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <t>A GENTLE STATUS ASK, not a new question - we know this is already with you and we are not chasing.
-Eight of our tests cover filter buttons on the Parts pages and the Reports pages. They were written from the designs back in July, and they are parked because that part of the product is not built yet and because your write-up for it has not arrived.
-To be straight with you: the write-up on its own will not unpark them - the feature still has to be built before anybody can run them. What the write-up does is let us finish the tests properly instead of leaving them resting on a design alone.
-Why we are asking: only so we can tell our own management honestly whether this is weeks away or months.</t>
+Eight of our tests cover filter buttons on the Parts pages and the Reports pages. They were written from the designs back in July, and they are parked because your write-up for them has not arrived.
+A CORRECTION WE OWE YOU: an earlier draft of this question also told you the feature was not built yet. That was our mistake. An engineering handover we were given today says the filter buttons on the eight Parts pages ARE built, and so are the ones on six reports - Shop Billing Efficiency, My Timesheets, Timesheet Activities, Notes, Reminders and Sales Tax - all waiting on one final code review.
+That same handover says several other reports are deliberately NOT being done in this piece of work. Our tests name a good many of those, which is a separate tidy-up on our side and not something you need to answer here.
+Why we are asking: so we can finish these tests against something you have written, rather than leaving them resting on a drawing alone - and so we can tell our own management honestly whether this is weeks away or months.</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -984,10 +985,11 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Nothing is stuck on this one and no test of ours is wrong today. We are asking so that we are not quietly relying on a note that disagrees with your own description.
-Your description says the day view keeps the WHOLE 24 HOURS there and scrollable, and simply scrolls itself so the start of the working day is on the left.
-A note on one of the design-review reports asks for something different: that the timeline show ONLY THE WORKING HOURS plus a little after them, with anything outside reached by scrolling. That note says it is tracked as a later improvement rather than for this release, which is why we have left our test alone.
-If the narrower version is meant for this release, your description needs changing first and then we will change the test to match.</t>
+          <t>Nothing is stuck on this one and no test of ours is wrong today. We are asking because two of your own documents now point in opposite directions.
+Your description says the day view keeps the WHOLE 24 HOURS there and scrollable, and simply scrolls itself so the start of the working day is on the left. That is still what it says today.
+The design review of 5 August asks for something different: that the timeline show ONLY THE WORKING HOURS plus a little after them, with anything outside reached by scrolling. That review lists it as IN SCOPE for this release, alongside the change that makes the day view open at the start of the working day.
+A CORRECTION WE OWE YOU: an earlier draft of this question told you that the narrower version was only a later improvement. That was our mistake - the review puts it in this release. We would rather correct it than have you answer on the strength of it.
+So your description was last changed on 7 August, two days AFTER that review, and it still says the full 24 hours. Only you can say which of the two you meant to stand. If the narrower version is meant for this release, your description needs changing first and then we will change the test to match.</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">

--- a/build/filters/questions-2026-08-06/Questions-for-Branko-Cicovic_Filters-and-Schedule_Friendly-Version_2026-08-06.xlsx
+++ b/build/filters/questions-2026-08-06/Questions-for-Branko-Cicovic_Filters-and-Schedule_Friendly-Version_2026-08-06.xlsx
@@ -471,8 +471,8 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hello Branko - this is everything we have open across TWO of your projects, FILTERS and SCHEDULE, gathered into one place so you can go through it in a single sitting instead of getting a trickle of separate messages. Twenty items; about twenty minutes if you go straight down the list. SHORT ANSWERS ARE PERFECT - a letter, or one line. Nothing here needs an essay.
-WHERE TO START. Section 1 is five questions that release tests which are stuck today - that is the part we are genuinely waiting on. Section 2 is eight ordinary decisions. Section 3 is six things only the engineering plan describes, and nothing of ours is waiting on those, so they can keep for a quiet moment. Section 4 is one typo-level heads-up with nothing to decide.
+          <t>Hello Branko - this is everything we have open across TWO of your projects, FILTERS and SCHEDULE, gathered into one place so you can go through it in a single sitting instead of getting a trickle of separate messages. Twenty-one items; about twenty minutes if you go straight down the list. SHORT ANSWERS ARE PERFECT - a letter, or one line. Nothing here needs an essay.
+WHERE TO START. Section 1 is five questions that release tests which are stuck today - that is the part we are genuinely waiting on. Section 2 is eight ordinary decisions. Section 3 is seven things only the engineering plan describes, and nothing of ours is waiting on those, so they can keep for a quiet moment. Section 4 is one typo-level heads-up with nothing to decide.
 ONE OF THESE IS OUR OWN FAULT and we are sorry: question 2 in Section 1 was written on 22 July and we never actually sent it to you. Two tests have been parked ever since waiting for an answer you were never asked for.
 Every question says which project it belongs to, because you look after Filters, Schedule and Global Search. And to be clear - we have not edited any of your tickets or your descriptions. Where two of your own documents disagree we simply say so and ask which one to keep.</t>
         </is>
@@ -1017,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1031,14 +1031,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Section 3 - six things only the engineering plan describes</t>
+          <t>Section 3 - seven things only the engineering plan describes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NOTHING OF OURS IS WAITING ON THIS TAB, so it can keep for a quiet moment. These six behaviours appear only in the engineering plan and nowhere in your own document. We are not going to turn an engineering note into something the product must do without your word - so each is either a decision for you or an item we close as out of scope.</t>
+          <t>NOTHING OF OURS IS WAITING ON THIS TAB, so it can keep for a quiet moment. These seven behaviours appear only in the engineering plan and nowhere in your own document. For the first six we are not going to turn an engineering note into something the product must do without your word - so each is either a decision for you or an item we close as out of scope. The seventh is different and says so: it is already covered by two of our tests and nothing is waiting on it - we are simply asking you to write the rule into your own description as well.</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SECTION 3 OF 4 - SIX ENGINEERING-PLAN-ONLY ITEMS. NO TEST IS BLOCKED BY THESE.</t>
+          <t>SECTION 3 OF 4 - SEVEN ENGINEERING-PLAN-ONLY ITEMS. NO TEST IS BLOCKED BY THESE.</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -1263,6 +1263,38 @@
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="300" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>FILTERS - the Work Orders list - using two different filter buttons at the same time</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>NOTHING OF OURS IS STUCK ON THIS ONE and we are not asking you to make a decision. We are asking you to write down in your own description something your engineers have already written down in theirs.
+The Work Orders list has five filter buttons: Status, Customer, Lead Technician, Service Advisor and Asset on Site.
+Your description says what each button does ON ITS OWN. For Status it says the list shows work orders matching ANY of the statuses you tick. For Customer it says the list shows work orders belonging to ANY of the customers you pick.
+What it never says is what the list should show when someone uses TWO DIFFERENT BUTTONS AT THE SAME TIME - for example ticking the status 'Estimate' and also picking the customer 'Smith'. We searched the whole of your current description and five earlier versions of it, and the rule is not there in any of them.
+Your engineers' own working notes DO state it: the buttons must narrow together, so the list shows only the work orders that match both. That is also what the product does today, and it is what two of our tests already check - so nothing is broken and nothing is waiting.
+Why we are raising it anyway: a rule that lives only in an engineering note is one edit away from being changed by accident, and nobody would notice. One sentence in your description settles it for good.</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>When someone ticks a status AND also picks a customer, what should the list show?</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>A) ONLY the work orders that match BOTH - status 'Estimate' AND customer 'Smith'. (This is what your engineers' notes say and what the product does today. If you pick A, please add a sentence saying so to your description - nothing of ours needs to change.)
+B) Something else - please describe it. (Then two of our tests are wrong and we will correct them.)</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1384,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1957,134 +1989,190 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Tab 3</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Filters - what the list should show when two DIFFERENT filter buttons are used at once (for example status Estimate + customer Smith)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-11, from build/filters/c29600-sourcing-2026-08-11/FINDINGS.md. NOT a blocked decision and NOT an undecided product question - a DOCUMENTATION GAP. The rule IS decided and IS written down, in the engineering technical design; it is his own product description that is silent. Framed to him accordingly (Rule 55).</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>NO case is held on this. TWO cases assert the rule and both are CORRECT as written - FLT-COMBO-01 (C29600, AUTOMATION: READY, TestRail custom_atmstatus = 3 AUTOMATED) and FLT-API-08 (C29632, AUTOMATION: READY, custom_atmstatus = 1). Both had their refs and provenance corrected on 2026-08-11 to cite the technical design; NEITHER had any assertion, step or expected outcome changed.</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>C29600 https://shopview.testrail.io/index.php?/cases/view/29600 · C29632 https://shopview.testrail.io/index.php?/cases/view/29632</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-11 against Filters Confluence page 572030978 at VERSION 19 (HTTP 200), and against versions 4, 12, 17 and 18. The rule for combining two DIFFERENT filters is absent from all five. Boolean 'AND' appears EXACTLY ONCE in the whole specification, at S13-R10 - 'Search and filters are additive (AND)' - which is search-versus-filters, not filter-versus-filter. S2-R2 and S3-R6 give OR *within* one filter ('matching any of the selected statuses' / 'belonging to any of the selected customers'). S8-R3, which C29600 and C29632 used to cite for this, is the EMPTY-STATE requirement and does not define the combination. All 14 epic stories (SV-8786 to SV-8799) were read live including comments: not one acceptance criterion states the result of combining two different filters. THE RULE IS STATED in the engineering technical design, build/filters/tech-plan-2026-07-29/TechPlan-AppWide-Filter-Redesign.md - §1.8 verbatim '...return the right WOs and AND across fields' (line 323) and §0.3 verbatim 'Same-field filters are grouped and OR'd ... repeated eq on one field is a de-facto IN' (line 218). That document is UNDATED internally and records 'Spec baseline: v1.3' (line 124), so it is a PARTIAL currency source.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>A -&gt; nothing of ours changes; he adds one sentence to his description and the two cases' provenance is re-stamped to name it instead of the technical design. B -&gt; both cases are wrong on their headline assertion, both must be corrected, and VLAD MUST BE TOLD because C29600 is flagged AUTOMATED in TestRail. Standing Rule 57's OPEN question - whether a technical design carries PRD-level authority on product behaviour, or whether Rule 30's 'informs but never overrules' still holds - governs these two cases as well as the nine in class C-3 of build/unsourced-cases-2026-08-11/CANDIDATES.md, so eleven in total. That question is the QA lead's, not Branko's, and is NOT on this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>HONESTY AND METHOD NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>THIS IS THE FRIENDLY, FORWARD-AS-IS VERSION of Questions-for-Branko-Cicovic_Filters-and-Schedule_2026-08-06.xlsx, produced on the QA lead's instruction: "Give me the friendly and easy to read and understandable files for Chris and Branko." 20 of the 21 items are carried over with their substance unchanged. What changed: a short warm opening note, REORDERING BY WHAT TO DO FIRST (five items that release stuck tests, then eight ordinary decisions, then the six engineering-plan-only items nothing is waiting on, then one heads-up with nothing to decide) with the headings and tab names saying so, and shorter sentences. The six engineering-only items and the pointer heads-up are IMPORTED verbatim from gen_branko_sheet.py so their wording cannot drift.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>ONE ITEM WAS REMOVED FROM THE READER-FACING SHEET, AND THIS IS WHY. The removed item asked whether the EXACT SHAPE OF THE REPORTS PAGE WEB ADDRESS (the date-range URL contract) is something we should be testing. HIS OWN SPECIFICATION ALREADY STATES IT, verbatim, in the "Reports Filters" part of the scope section: "The selected range is reflected in the URL (e.g., range=custom&amp;from=2026-04-01&amp;to=2026-04-25) so a filtered report is shareable". VERIFIED LIVE FOR THIS PASS - Confluence page 572030978, VERSION 19, HTTP 200, published 2026-08-06T11:48:47Z; the sentence is present in the live body (one occurrence). Sending it would have re-asked a question his own document answers - the exact embarrassment Rule 55 exists to prevent, and one this project has already had once. SO THE ROW IS OFF THE SHEET and the sheet is 20 items, not 21.</t>
+          <t>THIS IS THE FRIENDLY, FORWARD-AS-IS VERSION of Questions-for-Branko-Cicovic_Filters-and-Schedule_2026-08-06.xlsx, produced on the QA lead's instruction: "Give me the friendly and easy to read and understandable files for Chris and Branko." 20 of the 21 items are carried over with their substance unchanged. What changed: a short warm opening note, REORDERING BY WHAT TO DO FIRST (five items that release stuck tests, then eight ordinary decisions, then the six engineering-plan-only items nothing is waiting on, then one heads-up with nothing to decide) with the headings and tab names saying so, and shorter sentences. The six engineering-only items and the pointer heads-up are IMPORTED verbatim from gen_branko_sheet.py so their wording cannot drift.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>⚠️ CORRECTION OWED TO OUR OWN RECORD, FLAGGED NOT REWRITTEN. The earlier sheet's QA tab says of that item: "Filters v19 section 4 and S11-R1 say nothing about the address format". That is true of those two places and MISSES THE SCOPE-SECTION BULLET quoted above, which does state the shape. VLAD WAS RIGHT ON THAT ROW (row 8 of his eleven-row Filters coverage-gap table), and our recorded verdict in build/filters/vlad-gap-review-2026-08-06/ROW-BY-ROW.md NEEDS CORRECTING. It was deliberately NOT edited by this pass - that file is out of scope here, and silently rewriting a recorded verdict is not ours to do (Rules 33 and 44). THE QA LEAD OWES THAT ONE-ROW CORRECTION. There is also a real coverage consequence: the shape IS documented, so it is now authorable as a test rather than an open product question - which needs authorisation, and nothing was authored.</t>
+          <t>ONE ITEM WAS REMOVED FROM THE READER-FACING SHEET, AND THIS IS WHY. The removed item asked whether the EXACT SHAPE OF THE REPORTS PAGE WEB ADDRESS (the date-range URL contract) is something we should be testing. HIS OWN SPECIFICATION ALREADY STATES IT, verbatim, in the "Reports Filters" part of the scope section: "The selected range is reflected in the URL (e.g., range=custom&amp;from=2026-04-01&amp;to=2026-04-25) so a filtered report is shareable". VERIFIED LIVE FOR THIS PASS - Confluence page 572030978, VERSION 19, HTTP 200, published 2026-08-06T11:48:47Z; the sentence is present in the live body (one occurrence). Sending it would have re-asked a question his own document answers - the exact embarrassment Rule 55 exists to prevent, and one this project has already had once. SO THE ROW IS OFF THE SHEET and the sheet is 20 items, not 21. [SUPERSEDED 2026-08-11 ON THE COUNT ONLY - the removal itself stands and the reasoning above is unchanged; the sheet is 21 items again because a NEW item was added on 2026-08-11. See the next note.]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>THE EARLIER WORKBOOK IS SUPERSEDED, NOT DELETED. Both pairs sit in this folder. Send THIS one; the earlier pair is kept as the record of what was verified and when. NOTE THAT THE EARLIER PAIR STILL CARRIES THE URL QUESTION as its Filters item 3 - so if an old file goes out by mistake, that question goes with it. The rows and notes below are IMPORTED from gen_branko_sheet.py at build time so the mapping cannot drift; the URL item's own mapping row is carried below re-labelled as REMOVED, rather than deleted, so the decision stays auditable.</t>
+          <t>⚠️ ADDED 2026-08-11 - ONE NEW ITEM, TAKING THE SHEET FROM 20 BACK TO 21: the FILTERS CROSS-FILTER DOCUMENTATION GAP, appended as item 7 of Section 3. WHY IT IS IN SECTION 3: that section is exactly "behaviours only the engineering plan describes", and this is one - the rule that two DIFFERENT filter buttons narrow together is in the engineering technical design and in no version of his product description. WHY IT IS FRAMED DIFFERENTLY FROM THE OTHER SIX: the other six are candidate coverage awaiting his word, whereas this rule is already correctly covered by C29600 and C29632, because the technical design is an authoritative source under Standing Rule 57(d3). So it is put to him as a DOCUMENTATION GAP - his own engineers state it, his own description does not - and expressly NOT as a decision he has failed to make (Rule 55). NOTHING OF OURS IS BLOCKED ON IT and the row says so on its face, so he is not misled into thinking it is urgent. DUPLICATE CHECK RUN BEFORE ADDING IT (Rule 55): both markdown files, the README and EVERY XML part of BOTH workbooks were searched for 29600, 29632, 'multi-criteria', 'matching both' and 'two different filter' - ZERO hits in all of them, so it duplicates nothing. This also CORRECTS our own record: build/unsourced-cases-2026-08-11/CANDIDATES.md states C29600 is already on Branko's sheet; IT WAS NOT. Source: build/filters/c29600-sourcing-2026-08-11/FINDINGS.md; the accompanying TestRail recording fix is build/filters/c29600-fix-2026-08-11/.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>STILL OWED FROM THE EARLIER PASS AND NOT DONE HERE (both out of scope for this task): the 2026-08-05 Branko workbook in build/branko-questions-2026-08-05/ should be marked SUPERSEDED so an old one cannot go out by mistake; and CLAUDE.md plus build/OUTSTANDING-ITEMS-REGISTER.md still name the Schedule specification at version 23 when it is at 25.</t>
+          <t>NOTHING WAS SENT TO BRANKO. The QA lead's standing instruction is that nothing goes to a PO until our own work is done, so this remains a DRAFT. No Jira issue was created or edited by the 2026-08-11 pass either - the creation hold at the tail of Standing Rule 62 stands.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>NO OTHER SOURCE WAS RE-FETCHED AND NONE NEEDED TO BE. The content was verified live earlier on 2026-08-06 (Filters specification version 19, Schedule specification version 25) and this pass only rewrote the presentation and settled the one URL question above. The single live call made here was the read-only Confluence GET of page 572030978. NO TestRail write, no Jira call, no application call, and no case, ticket or specification was edited by anyone in this pass.</t>
+          <t>⚠️ CORRECTION OWED TO OUR OWN RECORD, FLAGGED NOT REWRITTEN. The earlier sheet's QA tab says of that item: "Filters v19 section 4 and S11-R1 say nothing about the address format". That is true of those two places and MISSES THE SCOPE-SECTION BULLET quoted above, which does state the shape. VLAD WAS RIGHT ON THAT ROW (row 8 of his eleven-row Filters coverage-gap table), and our recorded verdict in build/filters/vlad-gap-review-2026-08-06/ROW-BY-ROW.md NEEDS CORRECTING. It was deliberately NOT edited by this pass - that file is out of scope here, and silently rewriting a recorded verdict is not ours to do (Rules 33 and 44). THE QA LEAD OWES THAT ONE-ROW CORRECTION. There is also a real coverage consequence: the shape IS documented, so it is now authorable as a test rather than an open product question - which needs authorisation, and nothing was authored.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>ADDENDUM 2026-08-06 - FOUR SCHEDULE ITEMS ADDED, TAKING THE SHEET FROM 17 TO 21. They come from build/schedule/spec-v25-2026-08-06/QUESTIONS-FOR-BRANKO.md, the Schedule spec v23 -&gt; v25 diff. They are APPENDED as Schedule items 5-8 rather than re-ordered into the tab, so the established structure and the carried-forward wording are untouched (Rule 16); the tab note names items 5 and 6 as the decisive ones so their importance is still visible on the reader tab. TWO OF THEM EACH DECIDE A VERDICT: item 5 decides what C30041 should assert, item 6 decides whether C30012 passes or fails. Nothing was applied to TestRail - no case was edited, and the HOLDs those two items imply are PROPOSED in PROPOSED-CHANGES.md, not written.</t>
+          <t>THE EARLIER WORKBOOK IS SUPERSEDED, NOT DELETED. Both pairs sit in this folder. Send THIS one; the earlier pair is kept as the record of what was verified and when. NOTE THAT THE EARLIER PAIR STILL CARRIES THE URL QUESTION as its Filters item 3 - so if an old file goes out by mistake, that question goes with it. The rows and notes below are IMPORTED from gen_branko_sheet.py at build time so the mapping cannot drift; the URL item's own mapping row is carried below re-labelled as REMOVED, rather than deleted, so the decision stays auditable.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>ONE OF THE FOUR SOURCE QUESTIONS WAS DELIBERATELY LEFT OFF, AND THIS IS THE REASON (Rule 55: ask what is unclear; it does not say invent an ask). The source file's Q2b asked what the word "labor" means in v25's new phrase "labor/status figures" - the number of HOURS or a MONEY amount. It is NOT asked, on two grounds, both checked rather than assumed. FIRST, HE HAS ALREADY ANSWERED IT IN HIS OWN WORDS: SV-8829, 2026-08-06T04:31:05-0500, verbatim "for work order lines we just show estimate and status badge, there shouldn't be totals" - which, with his 22 July no-money-on-the-Schedule ruling, says plainly that no money appears. SECOND, THE SOURCE FILE ITSELF RECORDS THAT NEITHER ANSWER CHANGES THE CASE: "Neither answer changes the case's substance; A confirms it as written." So it would have cost a PO round trip for zero test consequence - and re-asking something a source has already settled is the exact embarrassment this project has had once already. ITS ONE GENUINELY LIVE CONSEQUENCE IS ON THE SHEET as Schedule item 7: that his STORY and his SPEC now disagree (`labor/total` vs `labor/status`), which is a fork with a real answer and a named owner. The residual ambiguity is in OUR OWN text - C30011 uses "labor" for both hours and money in one expected result - and that is an internal wording repair, not a question for a product owner.</t>
+          <t>STILL OWED FROM THE EARLIER PASS AND NOT DONE HERE (both out of scope for this task): the 2026-08-05 Branko workbook in build/branko-questions-2026-08-05/ should be marked SUPERSEDED so an old one cannot go out by mistake; and CLAUDE.md plus build/OUTSTANDING-ITEMS-REGISTER.md still name the Schedule specification at version 23 when it is at 25.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>THE DESIGN-AUTHORITY QUESTION WAS DELIBERATELY *NOT* ADDED AS A NEW ROW, ON THE QA LEAD'S INSTRUCTION AND BECAUSE IT WOULD HAVE BEEN A DUPLICATE. The source file's Q4 is a two-part item. Its PRODUCT half - which drawing of the Schedule is the one to work from - is ALREADY Schedule item 4 on this very sheet, and asking it twice inside one workbook would be the drip Rule 55 exists to prevent, in miniature. Its PROCESS half - whether a design may outrank the written description in OUR OWN method - is a decision for the QA LEAD, not for Branko, and has been put to him separately. Branko is asked which drawing is canonical; he is not asked to rule on our sourcing rules.</t>
+          <t>NO OTHER SOURCE WAS RE-FETCHED AND NONE NEEDED TO BE. The content was verified live earlier on 2026-08-06 (Filters specification version 19, Schedule specification version 25) and this pass only rewrote the presentation and settled the one URL question above. The single live call made here was the read-only Confluence GET of page 572030978. NO TestRail write, no Jira call, no application call, and no case, ticket or specification was edited by anyone in this pass.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>WHY ONE FILE AND NOT TWO (Standing Rule 55). build/branko-questions-2026-08-05/ holds a 13-item Branko sheet that is READY TO SEND and WAS NEVER SENT (register row C4). Producing a second sheet without absorbing it would leave the QA lead holding two unsent sheets for the same person - the exact 'drip of separate asks' Rule 55 exists to prevent. So this workbook CARRIES FORWARD all 13 of its items and adds 8 new ones = 21 (4 added when it was first built, and 4 more Schedule items added later the same day from the spec's move to version 25). ⚠️ ACTION NEEDED FROM THE QA LEAD: the 2026-08-05 workbook should be marked SUPERSEDED so an old one cannot go out by mistake. It was NOT edited by this pass, because this task was scoped to write only inside build/filters/questions-2026-08-06/ and build/report-suite/questions-2026-08-06/.</t>
+          <t>ADDENDUM 2026-08-06 - FOUR SCHEDULE ITEMS ADDED, TAKING THE SHEET FROM 17 TO 21. They come from build/schedule/spec-v25-2026-08-06/QUESTIONS-FOR-BRANKO.md, the Schedule spec v23 -&gt; v25 diff. They are APPENDED as Schedule items 5-8 rather than re-ordered into the tab, so the established structure and the carried-forward wording are untouched (Rule 16); the tab note names items 5 and 6 as the decisive ones so their importance is still visible on the reader tab. TWO OF THEM EACH DECIDE A VERDICT: item 5 decides what C30041 should assert, item 6 decides whether C30012 passes or fails. Nothing was applied to TestRail - no case was edited, and the HOLDs those two items imply are PROPOSED in PROPOSED-CHANGES.md, not written.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>HOW DRIFT WAS PREVENTED: every carried-forward reader-facing row is IMPORTED from the 2026-08-05 generator's own TAB1/TAB2/TAB3 lists at build time, not retyped. So the 13 carried items are byte-identical to the rows that sheet carried - the same technique the 2026-08-04 Chris consolidation used. Only the 8 new items and the tab notes are new text.</t>
+          <t>ONE OF THE FOUR SOURCE QUESTIONS WAS DELIBERATELY LEFT OFF, AND THIS IS THE REASON (Rule 55: ask what is unclear; it does not say invent an ask). The source file's Q2b asked what the word "labor" means in v25's new phrase "labor/status figures" - the number of HOURS or a MONEY amount. It is NOT asked, on two grounds, both checked rather than assumed. FIRST, HE HAS ALREADY ANSWERED IT IN HIS OWN WORDS: SV-8829, 2026-08-06T04:31:05-0500, verbatim "for work order lines we just show estimate and status badge, there shouldn't be totals" - which, with his 22 July no-money-on-the-Schedule ruling, says plainly that no money appears. SECOND, THE SOURCE FILE ITSELF RECORDS THAT NEITHER ANSWER CHANGES THE CASE: "Neither answer changes the case's substance; A confirms it as written." So it would have cost a PO round trip for zero test consequence - and re-asking something a source has already settled is the exact embarrassment this project has had once already. ITS ONE GENUINELY LIVE CONSEQUENCE IS ON THE SHEET as Schedule item 7: that his STORY and his SPEC now disagree (`labor/total` vs `labor/status`), which is a fork with a real answer and a named owner. The residual ambiguity is in OUR OWN text - C30011 uses "labor" for both hours and money in one expected result - and that is an internal wording repair, not a question for a product owner.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>SV-8876 IS DELIBERATELY NOT ON THIS SHEET, AND THE BRIEF FOR THIS TASK WAS WRONG ABOUT IT. The brief listed it as "Ahtasham's clarification question, still his to answer", and CLAUDE.md's Filters section says "Branko owes SV-8876". READ LIVE FROM JIRA 2026-08-06: SV-8876 is a Task, status DONE, resolution Done, resolved 2026-08-05T08:38:16-0500, parent SV-8785, reporter Ahtasham Amjad. He CLOSED IT HIMSELF, with one comment, verbatim: "closing this as it was a gap with test case , I've updated the test case here &gt;&gt;https://shopview.testrail.io/index.php?/cases/view/29557 And created a story defect &gt;&gt; as the build is not behaving as per PRD". Putting it in front of Branko would have re-asked a closed question - the exact embarrassment this project has already had once. THE HALF THAT IS GENUINELY STILL HIS is the narrower one and IS on the sheet, as Filters item 5: did he want the buttons on one row, in which case the developer job should be cancelled? SEPARATE POINT FOR THE QA LEAD, NOT FOR BRANKO: that comment says Ahtasham EDITED OUR CASE C29557. Under Rule 38 we do not touch his cases and he should not be editing ours; this is reported, not acted on.</t>
+          <t>THE DESIGN-AUTHORITY QUESTION WAS DELIBERATELY *NOT* ADDED AS A NEW ROW, ON THE QA LEAD'S INSTRUCTION AND BECAUSE IT WOULD HAVE BEEN A DUPLICATE. The source file's Q4 is a two-part item. Its PRODUCT half - which drawing of the Schedule is the one to work from - is ALREADY Schedule item 4 on this very sheet, and asking it twice inside one workbook would be the drip Rule 55 exists to prevent, in miniature. Its PROCESS half - whether a design may outrank the written description in OUR OWN method - is a decision for the QA LEAD, not for Branko, and has been put to him separately. Branko is asked which drawing is canonical; he is not asked to rule on our sourcing rules.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>THE FILTERS SPEC MOVED TO VERSION 19 THIS MORNING AND NO QUESTION WAS MANUFACTURED FROM IT. Page 572030978, version 19, 2026-08-06T11:48:47Z. Its visible change on the filter bar is S1-R3, verbatim: "Each chip displays a leading type-icon identifying the filter, the filter name, and a chevron icon indicating it opens a dropdown". THAT IS CLEAR ENOUGH TO TEST - a tester can check that each chip carries a leading icon plus a chevron, and which specific icon belongs to which chip comes from the design node the spec links. So NO ROW WAS ADDED for it (Rule 55 says ask what is unclear; it does not say invent an ask). What v19 did NOT do is resolve anything on this sheet: S9-R2 and S9-R3 are unchanged, and the S12-R2 cross-reference is still wrong. ⚠️ OWED: a proper v18 -&gt; v19 diff. This pass checked the points the sheet depends on, not the whole document, and does not claim to have diffed it.</t>
+          <t>WHY ONE FILE AND NOT TWO (Standing Rule 55). build/branko-questions-2026-08-05/ holds a 13-item Branko sheet that is READY TO SEND and WAS NEVER SENT (register row C4). Producing a second sheet without absorbing it would leave the QA lead holding two unsent sheets for the same person - the exact 'drip of separate asks' Rule 55 exists to prevent. So this workbook CARRIES FORWARD all 13 of its items and adds 8 new ones = 21 (4 added when it was first built, and 4 more Schedule items added later the same day from the spec's move to version 25). ⚠️ ACTION NEEDED FROM THE QA LEAD: the 2026-08-05 workbook should be marked SUPERSEDED so an old one cannot go out by mistake. It was NOT edited by this pass, because this task was scoped to write only inside build/filters/questions-2026-08-06/ and build/report-suite/questions-2026-08-06/.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>THE SCHEDULE v23 -&gt; v25 DIFF HAS SINCE BEEN DONE, AND THIS ADDENDUM IS ITS OUTPUT - so the warning that stood here ("we have not diffed it") IS NOW OUT OF DATE and is corrected rather than deleted. Page 713031682 is at VERSION 25 (2026-08-06T09:13:51Z, re-confirmed live for this addendum); CLAUDE.md and build/OUTSTANDING-ITEMS-REGISTER.md still name version 23, and NEITHER WAS EDITED (out of scope for this pass - the record correction is owed). The diff lives at build/schedule/spec-v25-2026-08-06/SPEC-DIFF.md: 2 requirements changed, 1 governing-source change that is not a page edit, 3 cases affected. Its four reader-facing questions are Schedule items 5-8 of this sheet. Also re-confirmed by that diff and unchanged in v25: both shop-closure sentences survive, both click-menu wordings survive, and all six engineering-only topics are still absent - so items 1-3 and tab 3 stand exactly as written.</t>
+          <t>HOW DRIFT WAS PREVENTED: every carried-forward reader-facing row is IMPORTED from the 2026-08-05 generator's own TAB1/TAB2/TAB3 lists at build time, not retyped. So the 13 carried items are byte-identical to the rows that sheet carried - the same technique the 2026-08-04 Chris consolidation used. Only the 8 new items and the tab notes are new text.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>WORDING RULES APPLIED (Standing Rules 7 and 55): every reader-facing question row names the PROJECT (Filters or Schedule) and the SCREEN, because Branko owns THREE projects - Filters, Schedule and Global Search - so a row read on its own, days later, on a phone must still be unambiguous. Story and epic keys appear in plain form only where they orient him. No case IDs, no requirement anchors, no technical terms and not the word VIU appear anywhere he reads. Each question is a plain A/B/C with a blank for the answer, and each carries a one-line reason so the consequence is visible.</t>
+          <t>SV-8876 IS DELIBERATELY NOT ON THIS SHEET, AND THE BRIEF FOR THIS TASK WAS WRONG ABOUT IT. The brief listed it as "Ahtasham's clarification question, still his to answer", and CLAUDE.md's Filters section says "Branko owes SV-8876". READ LIVE FROM JIRA 2026-08-06: SV-8876 is a Task, status DONE, resolution Done, resolved 2026-08-05T08:38:16-0500, parent SV-8785, reporter Ahtasham Amjad. He CLOSED IT HIMSELF, with one comment, verbatim: "closing this as it was a gap with test case , I've updated the test case here &gt;&gt;https://shopview.testrail.io/index.php?/cases/view/29557 And created a story defect &gt;&gt; as the build is not behaving as per PRD". Putting it in front of Branko would have re-asked a closed question - the exact embarrassment this project has already had once. THE HALF THAT IS GENUINELY STILL HIS is the narrower one and IS on the sheet, as Filters item 5: did he want the buttons on one row, in which case the developer job should be cancelled? SEPARATE POINT FOR THE QA LEAD, NOT FOR BRANKO: that comment says Ahtasham EDITED OUR CASE C29557. Under Rule 38 we do not touch his cases and he should not be editing ours; this is reported, not acted on.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>SOURCE-CURRENCY (Standing Rules 31 and 59), fetched LIVE and re-read immediately before writing, 2026-08-06: Filters spec page 572030978 = VERSION 19, HTTP 200 (in-body field still reads "Version: 1.6" - the Rule-31(a) trap; the CONFLUENCE number is the one used). Schedule spec page 713031682 = VERSION 25, HTTP 200, and STALE against our records at 23. Jira read live for SV-8876, SV-8825, SV-8915, SV-8916, SV-8917. TestRail read live for all 114 Filters cases. Designs = PARTIAL, and which artefact is canonical is Schedule item 4 on this very sheet. ADDENDUM, 2026-08-06: for the four new Schedule items the Schedule spec was RE-FETCHED live (page 713031682, version 25, HTTP 200, by Branko Cicovic at 09:13:51Z) and every sentence they rest on was searched in its body; JIRA was read live and read-only for SV-8686, SV-8695, SV-8829, SV-8874, SV-8837 and SV-8915; and FOUR SCHEDULE CASES WERE PULLED LIVE FROM TESTRAIL - C30041, C30012, C30011 and C30001, all HTTP 200, titles, refs and automation markers read from the live cases rather than from our records. So the earlier line saying "Schedule cases were NOT re-pulled this pass" now holds only for the THREE HELD C-ids on items 1-3 (C29983, C30089, C43555), which still come from committed records and are still cited as such.</t>
+          <t>THE FILTERS SPEC MOVED TO VERSION 19 THIS MORNING AND NO QUESTION WAS MANUFACTURED FROM IT. Page 572030978, version 19, 2026-08-06T11:48:47Z. Its visible change on the filter bar is S1-R3, verbatim: "Each chip displays a leading type-icon identifying the filter, the filter name, and a chevron icon indicating it opens a dropdown". THAT IS CLEAR ENOUGH TO TEST - a tester can check that each chip carries a leading icon plus a chevron, and which specific icon belongs to which chip comes from the design node the spec links. So NO ROW WAS ADDED for it (Rule 55 says ask what is unclear; it does not say invent an ask). What v19 did NOT do is resolve anything on this sheet: S9-R2 and S9-R3 are unchanged, and the S12-R2 cross-reference is still wrong. ⚠️ OWED: a proper v18 -&gt; v19 diff. This pass checked the points the sheet depends on, not the whole document, and does not claim to have diffed it.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>THE BUILD WAS NOT OBSERVED (Standing Rules 12, 49, 60). The shared QA sign-in is dead - a read-only probe returned HTTP 401 {"error":"sso_required"} - and quick-login and switch-user were deliberately NOT called, because both rotate the shared session and would sign concurrent workers out of the other branches. BOTH BRANCHES HAVE ALSO REDEPLOYED: sv8785.qa.shopview.com now reads app-version v3.4.2-280ca5a (last-modified Thu 06 Aug 2026 09:37:49 GMT) where the Filters passes ran on v3.4.2-d00239b. So every build-side sentence quoted to Branko - the Status chip behaving as the description says, the filter bar on one row, the capital F - comes from a build that no longer exists, and is worded to him as what the product does rather than as a fresh measurement. All Filters and Schedule verdicts remain PROVISIONAL and the Rule-49 queues are OPEN.</t>
+          <t>THE SCHEDULE v23 -&gt; v25 DIFF HAS SINCE BEEN DONE, AND THIS ADDENDUM IS ITS OUTPUT - so the warning that stood here ("we have not diffed it") IS NOW OUT OF DATE and is corrected rather than deleted. Page 713031682 is at VERSION 25 (2026-08-06T09:13:51Z, re-confirmed live for this addendum); CLAUDE.md and build/OUTSTANDING-ITEMS-REGISTER.md still name version 23, and NEITHER WAS EDITED (out of scope for this pass - the record correction is owed). The diff lives at build/schedule/spec-v25-2026-08-06/SPEC-DIFF.md: 2 requirements changed, 1 governing-source change that is not a page edit, 3 cases affected. Its four reader-facing questions are Schedule items 5-8 of this sheet. Also re-confirmed by that diff and unchanged in v25: both shop-closure sentences survive, both click-menu wordings survive, and all six engineering-only topics are still absent - so items 1-3 and tab 3 stand exactly as written.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>WORDING RULES APPLIED (Standing Rules 7 and 55): every reader-facing question row names the PROJECT (Filters or Schedule) and the SCREEN, because Branko owns THREE projects - Filters, Schedule and Global Search - so a row read on its own, days later, on a phone must still be unambiguous. Story and epic keys appear in plain form only where they orient him. No case IDs, no requirement anchors, no technical terms and not the word VIU appear anywhere he reads. Each question is a plain A/B/C with a blank for the answer, and each carries a one-line reason so the consequence is visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE-CURRENCY (Standing Rules 31 and 59), fetched LIVE and re-read immediately before writing, 2026-08-06: Filters spec page 572030978 = VERSION 19, HTTP 200 (in-body field still reads "Version: 1.6" - the Rule-31(a) trap; the CONFLUENCE number is the one used). Schedule spec page 713031682 = VERSION 25, HTTP 200, and STALE against our records at 23. Jira read live for SV-8876, SV-8825, SV-8915, SV-8916, SV-8917. TestRail read live for all 114 Filters cases. Designs = PARTIAL, and which artefact is canonical is Schedule item 4 on this very sheet. ADDENDUM, 2026-08-06: for the four new Schedule items the Schedule spec was RE-FETCHED live (page 713031682, version 25, HTTP 200, by Branko Cicovic at 09:13:51Z) and every sentence they rest on was searched in its body; JIRA was read live and read-only for SV-8686, SV-8695, SV-8829, SV-8874, SV-8837 and SV-8915; and FOUR SCHEDULE CASES WERE PULLED LIVE FROM TESTRAIL - C30041, C30012, C30011 and C30001, all HTTP 200, titles, refs and automation markers read from the live cases rather than from our records. So the earlier line saying "Schedule cases were NOT re-pulled this pass" now holds only for the THREE HELD C-ids on items 1-3 (C29983, C30089, C43555), which still come from committed records and are still cited as such.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>THE BUILD WAS NOT OBSERVED (Standing Rules 12, 49, 60). The shared QA sign-in is dead - a read-only probe returned HTTP 401 {"error":"sso_required"} - and quick-login and switch-user were deliberately NOT called, because both rotate the shared session and would sign concurrent workers out of the other branches. BOTH BRANCHES HAVE ALSO REDEPLOYED: sv8785.qa.shopview.com now reads app-version v3.4.2-280ca5a (last-modified Thu 06 Aug 2026 09:37:49 GMT) where the Filters passes ran on v3.4.2-d00239b. So every build-side sentence quoted to Branko - the Status chip behaving as the description says, the filter bar on one row, the capital F - comes from a build that no longer exists, and is worded to him as what the product does rather than as a fresh measurement. All Filters and Schedule verdicts remain PROVISIONAL and the Rule-49 queues are OPEN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>NOTHING HAS BEEN WRITTEN ANYWHERE. This sheet is a draft for the QA lead to send. Read-only on TestRail (get_sections, get_cases), on Confluence (GET content) and on Jira (GET issue). No TestRail write, no Jira write, no case edit, no run write, no application call. CLAUDE.md, build/OUTSTANDING-ITEMS-REGISTER.md and build/APP-ACTIONS-PLAYBOOK.md were not touched, and neither was the 2026-08-05 Branko workbook.</t>
         </is>

--- a/build/filters/questions-2026-08-06/Questions-for-Branko-Cicovic_Filters-and-Schedule_Friendly-Version_2026-08-06.xlsx
+++ b/build/filters/questions-2026-08-06/Questions-for-Branko-Cicovic_Filters-and-Schedule_Friendly-Version_2026-08-06.xlsx
@@ -471,8 +471,8 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hello Branko - this is everything we have open across TWO of your projects, FILTERS and SCHEDULE, gathered into one place so you can go through it in a single sitting instead of getting a trickle of separate messages. Twenty-one items; about twenty minutes if you go straight down the list. SHORT ANSWERS ARE PERFECT - a letter, or one line. Nothing here needs an essay.
-WHERE TO START. Section 1 is five questions that release tests which are stuck today - that is the part we are genuinely waiting on. Section 2 is eight ordinary decisions. Section 3 is seven things only the engineering plan describes, and nothing of ours is waiting on those, so they can keep for a quiet moment. Section 4 is one typo-level heads-up with nothing to decide.
+          <t>Hello Branko - this is everything we have open across TWO of your projects, FILTERS and SCHEDULE, gathered into one place so you can go through it in a single sitting instead of getting a trickle of separate messages. Twenty-two items; about twenty minutes if you go straight down the list. SHORT ANSWERS ARE PERFECT - a letter, or one line. Nothing here needs an essay.
+WHERE TO START. Section 1 is five questions that release tests which are stuck today - that is the part we are genuinely waiting on. Section 2 is nine ordinary decisions. Section 3 is seven things only the engineering plan describes, and nothing of ours is waiting on those, so they can keep for a quiet moment. Section 4 is one typo-level heads-up with nothing to decide.
 ONE OF THESE IS OUR OWN FAULT and we are sorry: question 2 in Section 1 was written on 22 July and we never actually sent it to you. Two tests have been parked ever since waiting for an answer you were never asked for.
 Every question says which project it belongs to, because you look after Filters, Schedule and Global Search. And to be clear - we have not edited any of your tickets or your descriptions. Where two of your own documents disagree we simply say so and ask which one to keep.</t>
         </is>
@@ -690,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -704,7 +704,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Section 2 - eight ordinary decisions</t>
+          <t>Section 2 - nine ordinary decisions</t>
         </is>
       </c>
     </row>
@@ -1005,6 +1005,38 @@
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="300" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>SCHEDULE - the technician calendar - the Status filter on the work order list, when you want more than one status at a time</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Nothing is stuck on this one and no test of ours is wrong today. We are asking because we found one of our own tests claiming something your description does not say, and we have taken the claim out rather than leave it in.
+On the Schedule page there is a Filter panel, and one of its groups is Status. Your description lists what goes in that group - "all work order statuses currently supported in the app" - and it says that applying a filter narrows the list of work order cards.
+What it does not say, anywhere, is whether you can pick MORE THAN ONE status at the same time - for example Approved and Review together - and what the list should then show.
+Being straight with you about what we did: one of our tests had been claiming that choosing several statuses shows the work orders of all of them together. We could not find that in your description, in the story, in the design or in anything you have told us, so we have removed the claim. We have NOT replaced it with the opposite - we are not saying you can only pick one - because we do not know, and guessing either way would put words in your mouth.
+So the test now checks one status at a time, which is safe and true either way. If you tell us more than one is intended, we will add that back as a proper test and note that it came from you.</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Can more than one status be chosen in the Status filter at the same time, and if so what should the list show?</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>A) YES - you can pick several statuses, and the list shows the work orders of ALL the chosen statuses together.
+B) NO - only one status at a time; picking another replaces the first.
+C) Something else - please describe it.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1416,7 +1448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2031,148 +2063,197 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Tab 2</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Schedule - whether more than one status can be chosen in the Status filter, and what the work order list should then show</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-11, from build/schedule/followup-push-2026-08-11/. This is a COVERAGE GAP we created by removing an unsourced assertion, not a blocked decision. Framed to him as an ordinary decision, and it says on its face that nothing of ours is stuck (Rule 55).</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>NO case is held on this. ONE case is affected - SCH-FILT-03 (C29944, AUTOMATION: READY, TestRail custom_atmstatus = 1 NOT AUTOMATED at write time) - and it is CORRECT as it now stands. Its expected item 3, 'Choosing more than one status shows the work orders of all the chosen statuses together.', was REMOVED on 2026-08-11 and item 4 renumbered to 3. Its steps, preconditions, title, refs and provenance were NOT changed. The opposite was deliberately NOT asserted either: nothing claims multi-select is absent, because that is equally unsourced (Rules 25/42/57/58).</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>C29944 https://shopview.testrail.io/index.php?/cases/view/29944</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED LIVE 2026-08-11 before the removal. Schedule Confluence page 713031682 at VERSION 27 (HTTP 200, published 2026-08-07T15:01:20.801Z, 43,064 chars, body sha256 4c51fb72...), read at both the start and the end of the write window and byte-identical (Rule 59). §5.1 in full on this point is only: 'Status | All work order statuses currently supported in the app'. The words multi, multi-select, multiple, more than one, several, checkbox, one or more, combine, at once and simultane- appear in §5.1 ZERO times, in NONE of the 27 versions. Whole-document counts: 'multi-select' 0, 'multiple statuses' 0, 'more than one status' 0. The only 'Select multiple' in the specification is §4.3, the SCOPE PICKER turning line rows into checkboxes - a different feature. Story SV-8687 ('Work Order Sidebar &amp; Mini Calendar', QA Complete) was read live and independently: 'multi' 0, 'more than one' 0; its filter sentence is 'Filter groups: Assignment (Assigned/Unassigned), Status (all WO statuses), Priority (High/Medium/Low)'. The case's own authoring note has said since it was written: 'Single vs multi-select within a group is not pinned - confirm live.' The claim was introduced by our own 2026-08-05 repair pass, whose audit had scored the case clean minutes earlier - Rule 58's failure mode exactly.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>A -&gt; the assertion goes BACK, with a step that selects two statuses, cited to his answer with its date and file link (Rule 54), and the multi-status behaviour is covered again. B -&gt; nothing changes; C29944 is already correct, and we may add a small negative check that picking a second status replaces the first. EITHER WAY VLAD NEED NOT BE TOLD for this case - C29944 is custom_atmstatus = 1, not flagged AUTOMATED (Rule 65). UNTIL HE ANSWERS, multi-status filtering on the Schedule work order list is UNCOVERED, and that is the honest cost of the removal - recorded rather than hidden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>HONESTY AND METHOD NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>THIS IS THE FRIENDLY, FORWARD-AS-IS VERSION of Questions-for-Branko-Cicovic_Filters-and-Schedule_2026-08-06.xlsx, produced on the QA lead's instruction: "Give me the friendly and easy to read and understandable files for Chris and Branko." 20 of the 21 items are carried over with their substance unchanged. What changed: a short warm opening note, REORDERING BY WHAT TO DO FIRST (five items that release stuck tests, then eight ordinary decisions, then the six engineering-plan-only items nothing is waiting on, then one heads-up with nothing to decide) with the headings and tab names saying so, and shorter sentences. The six engineering-only items and the pointer heads-up are IMPORTED verbatim from gen_branko_sheet.py so their wording cannot drift.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>ONE ITEM WAS REMOVED FROM THE READER-FACING SHEET, AND THIS IS WHY. The removed item asked whether the EXACT SHAPE OF THE REPORTS PAGE WEB ADDRESS (the date-range URL contract) is something we should be testing. HIS OWN SPECIFICATION ALREADY STATES IT, verbatim, in the "Reports Filters" part of the scope section: "The selected range is reflected in the URL (e.g., range=custom&amp;from=2026-04-01&amp;to=2026-04-25) so a filtered report is shareable". VERIFIED LIVE FOR THIS PASS - Confluence page 572030978, VERSION 19, HTTP 200, published 2026-08-06T11:48:47Z; the sentence is present in the live body (one occurrence). Sending it would have re-asked a question his own document answers - the exact embarrassment Rule 55 exists to prevent, and one this project has already had once. SO THE ROW IS OFF THE SHEET and the sheet is 20 items, not 21. [SUPERSEDED 2026-08-11 ON THE COUNT ONLY - the removal itself stands and the reasoning above is unchanged; the sheet is 21 items again because a NEW item was added on 2026-08-11. See the next note.]</t>
+          <t>THIS IS THE FRIENDLY, FORWARD-AS-IS VERSION of Questions-for-Branko-Cicovic_Filters-and-Schedule_2026-08-06.xlsx, produced on the QA lead's instruction: "Give me the friendly and easy to read and understandable files for Chris and Branko." 20 of the 21 items are carried over with their substance unchanged. What changed: a short warm opening note, REORDERING BY WHAT TO DO FIRST (five items that release stuck tests, then nine ordinary decisions, then the six engineering-plan-only items nothing is waiting on, then one heads-up with nothing to decide) with the headings and tab names saying so, and shorter sentences. The six engineering-only items and the pointer heads-up are IMPORTED verbatim from gen_branko_sheet.py so their wording cannot drift.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>⚠️ ADDED 2026-08-11 - ONE NEW ITEM, TAKING THE SHEET FROM 20 BACK TO 21: the FILTERS CROSS-FILTER DOCUMENTATION GAP, appended as item 7 of Section 3. WHY IT IS IN SECTION 3: that section is exactly "behaviours only the engineering plan describes", and this is one - the rule that two DIFFERENT filter buttons narrow together is in the engineering technical design and in no version of his product description. WHY IT IS FRAMED DIFFERENTLY FROM THE OTHER SIX: the other six are candidate coverage awaiting his word, whereas this rule is already correctly covered by C29600 and C29632, because the technical design is an authoritative source under Standing Rule 57(d3). So it is put to him as a DOCUMENTATION GAP - his own engineers state it, his own description does not - and expressly NOT as a decision he has failed to make (Rule 55). NOTHING OF OURS IS BLOCKED ON IT and the row says so on its face, so he is not misled into thinking it is urgent. DUPLICATE CHECK RUN BEFORE ADDING IT (Rule 55): both markdown files, the README and EVERY XML part of BOTH workbooks were searched for 29600, 29632, 'multi-criteria', 'matching both' and 'two different filter' - ZERO hits in all of them, so it duplicates nothing. This also CORRECTS our own record: build/unsourced-cases-2026-08-11/CANDIDATES.md states C29600 is already on Branko's sheet; IT WAS NOT. Source: build/filters/c29600-sourcing-2026-08-11/FINDINGS.md; the accompanying TestRail recording fix is build/filters/c29600-fix-2026-08-11/.</t>
+          <t>ONE ITEM WAS REMOVED FROM THE READER-FACING SHEET, AND THIS IS WHY. The removed item asked whether the EXACT SHAPE OF THE REPORTS PAGE WEB ADDRESS (the date-range URL contract) is something we should be testing. HIS OWN SPECIFICATION ALREADY STATES IT, verbatim, in the "Reports Filters" part of the scope section: "The selected range is reflected in the URL (e.g., range=custom&amp;from=2026-04-01&amp;to=2026-04-25) so a filtered report is shareable". VERIFIED LIVE FOR THIS PASS - Confluence page 572030978, VERSION 19, HTTP 200, published 2026-08-06T11:48:47Z; the sentence is present in the live body (one occurrence). Sending it would have re-asked a question his own document answers - the exact embarrassment Rule 55 exists to prevent, and one this project has already had once. SO THE ROW IS OFF THE SHEET and the sheet is 20 items, not 21. [SUPERSEDED 2026-08-11 ON THE COUNT ONLY - the removal itself stands and the reasoning above is unchanged; the sheet is 21 items again because a NEW item was added on 2026-08-11. See the next note.]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>NOTHING WAS SENT TO BRANKO. The QA lead's standing instruction is that nothing goes to a PO until our own work is done, so this remains a DRAFT. No Jira issue was created or edited by the 2026-08-11 pass either - the creation hold at the tail of Standing Rule 62 stands.</t>
+          <t>⚠️ ADDED 2026-08-11 - ONE NEW ITEM, TAKING THE SHEET FROM 20 BACK TO 21: the FILTERS CROSS-FILTER DOCUMENTATION GAP, appended as item 7 of Section 3. WHY IT IS IN SECTION 3: that section is exactly "behaviours only the engineering plan describes", and this is one - the rule that two DIFFERENT filter buttons narrow together is in the engineering technical design and in no version of his product description. WHY IT IS FRAMED DIFFERENTLY FROM THE OTHER SIX: the other six are candidate coverage awaiting his word, whereas this rule is already correctly covered by C29600 and C29632, because the technical design is an authoritative source under Standing Rule 57(d3). So it is put to him as a DOCUMENTATION GAP - his own engineers state it, his own description does not - and expressly NOT as a decision he has failed to make (Rule 55). NOTHING OF OURS IS BLOCKED ON IT and the row says so on its face, so he is not misled into thinking it is urgent. DUPLICATE CHECK RUN BEFORE ADDING IT (Rule 55): both markdown files, the README and EVERY XML part of BOTH workbooks were searched for 29600, 29632, 'multi-criteria', 'matching both' and 'two different filter' - ZERO hits in all of them, so it duplicates nothing. This also CORRECTS our own record: build/unsourced-cases-2026-08-11/CANDIDATES.md states C29600 is already on Branko's sheet; IT WAS NOT. Source: build/filters/c29600-sourcing-2026-08-11/FINDINGS.md; the accompanying TestRail recording fix is build/filters/c29600-fix-2026-08-11/.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>⚠️ CORRECTION OWED TO OUR OWN RECORD, FLAGGED NOT REWRITTEN. The earlier sheet's QA tab says of that item: "Filters v19 section 4 and S11-R1 say nothing about the address format". That is true of those two places and MISSES THE SCOPE-SECTION BULLET quoted above, which does state the shape. VLAD WAS RIGHT ON THAT ROW (row 8 of his eleven-row Filters coverage-gap table), and our recorded verdict in build/filters/vlad-gap-review-2026-08-06/ROW-BY-ROW.md NEEDS CORRECTING. It was deliberately NOT edited by this pass - that file is out of scope here, and silently rewriting a recorded verdict is not ours to do (Rules 33 and 44). THE QA LEAD OWES THAT ONE-ROW CORRECTION. There is also a real coverage consequence: the shape IS documented, so it is now authorable as a test rather than an open product question - which needs authorisation, and nothing was authored.</t>
+          <t>⚠️ ADDED 2026-08-11 (SECOND ADDITION THAT DAY) - ONE MORE NEW ITEM, TAKING THE SHEET FROM 21 TO 22: the SCHEDULE STATUS-FILTER MULTI-SELECT question, appended as item 9 of Section 2. WHY SECTION 2 AND NOT SECTION 1: Section 1 is for questions that release tests stuck today, and NOTHING OF OURS IS STUCK on this - C29944 still runs, it simply no longer asserts what happens when two statuses are chosen. WHERE IT CAME FROM: build/schedule/followup-push-2026-08-11/ removed C29944's expected item 3, 'Choosing more than one status shows the work orders of all the chosen statuses together.', because NO source states it - §5.1 is silent in all 27 spec versions, story SV-8687 is silent, and the case's own authoring note has always said 'Single vs multi-select within a group is not pinned - confirm live'. The claim had been introduced by our OWN 2026-08-05 repair pass, which is Rule 58's failure mode exactly. WHAT WE DID NOT DO: we did not assert the opposite either - nothing now claims multi-select is absent, because that is equally unsourced (Rules 25/42/57). THE HONEST COST, STATED ON THE QA TAB AND NOT HIDDEN: until he answers, multi-status filtering on the Schedule work order list is UNCOVERED. DUPLICATE CHECK RUN BEFORE ADDING IT (Rule 55): both markdown files, the README and EVERY XML part of BOTH workbooks were searched for 29944, 'more than one status', 'multi-select', 'multiselect', 'multiple statuses', 'several statuses', 'Status group' and 'SCH-FILT' - ZERO hits in all of them, so it duplicates nothing. Prose counts in the opening note and the section headings were updated from 21 to 22 items and Section 2 from eight decisions to nine; the module docstring's 'eight ordinary decisions' is left as the record of what the 2026-08-06 reorder did.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>THE EARLIER WORKBOOK IS SUPERSEDED, NOT DELETED. Both pairs sit in this folder. Send THIS one; the earlier pair is kept as the record of what was verified and when. NOTE THAT THE EARLIER PAIR STILL CARRIES THE URL QUESTION as its Filters item 3 - so if an old file goes out by mistake, that question goes with it. The rows and notes below are IMPORTED from gen_branko_sheet.py at build time so the mapping cannot drift; the URL item's own mapping row is carried below re-labelled as REMOVED, rather than deleted, so the decision stays auditable.</t>
+          <t>NOTHING WAS SENT TO BRANKO. The QA lead's standing instruction is that nothing goes to a PO until our own work is done, so this remains a DRAFT. No Jira issue was created or edited by the 2026-08-11 pass either - the creation hold at the tail of Standing Rule 62 stands.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>STILL OWED FROM THE EARLIER PASS AND NOT DONE HERE (both out of scope for this task): the 2026-08-05 Branko workbook in build/branko-questions-2026-08-05/ should be marked SUPERSEDED so an old one cannot go out by mistake; and CLAUDE.md plus build/OUTSTANDING-ITEMS-REGISTER.md still name the Schedule specification at version 23 when it is at 25.</t>
+          <t>⚠️ CORRECTION OWED TO OUR OWN RECORD, FLAGGED NOT REWRITTEN. The earlier sheet's QA tab says of that item: "Filters v19 section 4 and S11-R1 say nothing about the address format". That is true of those two places and MISSES THE SCOPE-SECTION BULLET quoted above, which does state the shape. VLAD WAS RIGHT ON THAT ROW (row 8 of his eleven-row Filters coverage-gap table), and our recorded verdict in build/filters/vlad-gap-review-2026-08-06/ROW-BY-ROW.md NEEDS CORRECTING. It was deliberately NOT edited by this pass - that file is out of scope here, and silently rewriting a recorded verdict is not ours to do (Rules 33 and 44). THE QA LEAD OWES THAT ONE-ROW CORRECTION. There is also a real coverage consequence: the shape IS documented, so it is now authorable as a test rather than an open product question - which needs authorisation, and nothing was authored.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>NO OTHER SOURCE WAS RE-FETCHED AND NONE NEEDED TO BE. The content was verified live earlier on 2026-08-06 (Filters specification version 19, Schedule specification version 25) and this pass only rewrote the presentation and settled the one URL question above. The single live call made here was the read-only Confluence GET of page 572030978. NO TestRail write, no Jira call, no application call, and no case, ticket or specification was edited by anyone in this pass.</t>
+          <t>THE EARLIER WORKBOOK IS SUPERSEDED, NOT DELETED. Both pairs sit in this folder. Send THIS one; the earlier pair is kept as the record of what was verified and when. NOTE THAT THE EARLIER PAIR STILL CARRIES THE URL QUESTION as its Filters item 3 - so if an old file goes out by mistake, that question goes with it. The rows and notes below are IMPORTED from gen_branko_sheet.py at build time so the mapping cannot drift; the URL item's own mapping row is carried below re-labelled as REMOVED, rather than deleted, so the decision stays auditable.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>ADDENDUM 2026-08-06 - FOUR SCHEDULE ITEMS ADDED, TAKING THE SHEET FROM 17 TO 21. They come from build/schedule/spec-v25-2026-08-06/QUESTIONS-FOR-BRANKO.md, the Schedule spec v23 -&gt; v25 diff. They are APPENDED as Schedule items 5-8 rather than re-ordered into the tab, so the established structure and the carried-forward wording are untouched (Rule 16); the tab note names items 5 and 6 as the decisive ones so their importance is still visible on the reader tab. TWO OF THEM EACH DECIDE A VERDICT: item 5 decides what C30041 should assert, item 6 decides whether C30012 passes or fails. Nothing was applied to TestRail - no case was edited, and the HOLDs those two items imply are PROPOSED in PROPOSED-CHANGES.md, not written.</t>
+          <t>STILL OWED FROM THE EARLIER PASS AND NOT DONE HERE (both out of scope for this task): the 2026-08-05 Branko workbook in build/branko-questions-2026-08-05/ should be marked SUPERSEDED so an old one cannot go out by mistake; and CLAUDE.md plus build/OUTSTANDING-ITEMS-REGISTER.md still name the Schedule specification at version 23 when it is at 25.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>ONE OF THE FOUR SOURCE QUESTIONS WAS DELIBERATELY LEFT OFF, AND THIS IS THE REASON (Rule 55: ask what is unclear; it does not say invent an ask). The source file's Q2b asked what the word "labor" means in v25's new phrase "labor/status figures" - the number of HOURS or a MONEY amount. It is NOT asked, on two grounds, both checked rather than assumed. FIRST, HE HAS ALREADY ANSWERED IT IN HIS OWN WORDS: SV-8829, 2026-08-06T04:31:05-0500, verbatim "for work order lines we just show estimate and status badge, there shouldn't be totals" - which, with his 22 July no-money-on-the-Schedule ruling, says plainly that no money appears. SECOND, THE SOURCE FILE ITSELF RECORDS THAT NEITHER ANSWER CHANGES THE CASE: "Neither answer changes the case's substance; A confirms it as written." So it would have cost a PO round trip for zero test consequence - and re-asking something a source has already settled is the exact embarrassment this project has had once already. ITS ONE GENUINELY LIVE CONSEQUENCE IS ON THE SHEET as Schedule item 7: that his STORY and his SPEC now disagree (`labor/total` vs `labor/status`), which is a fork with a real answer and a named owner. The residual ambiguity is in OUR OWN text - C30011 uses "labor" for both hours and money in one expected result - and that is an internal wording repair, not a question for a product owner.</t>
+          <t>NO OTHER SOURCE WAS RE-FETCHED AND NONE NEEDED TO BE. The content was verified live earlier on 2026-08-06 (Filters specification version 19, Schedule specification version 25) and this pass only rewrote the presentation and settled the one URL question above. The single live call made here was the read-only Confluence GET of page 572030978. NO TestRail write, no Jira call, no application call, and no case, ticket or specification was edited by anyone in this pass.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>THE DESIGN-AUTHORITY QUESTION WAS DELIBERATELY *NOT* ADDED AS A NEW ROW, ON THE QA LEAD'S INSTRUCTION AND BECAUSE IT WOULD HAVE BEEN A DUPLICATE. The source file's Q4 is a two-part item. Its PRODUCT half - which drawing of the Schedule is the one to work from - is ALREADY Schedule item 4 on this very sheet, and asking it twice inside one workbook would be the drip Rule 55 exists to prevent, in miniature. Its PROCESS half - whether a design may outrank the written description in OUR OWN method - is a decision for the QA LEAD, not for Branko, and has been put to him separately. Branko is asked which drawing is canonical; he is not asked to rule on our sourcing rules.</t>
+          <t>ADDENDUM 2026-08-06 - FOUR SCHEDULE ITEMS ADDED, TAKING THE SHEET FROM 17 TO 21. They come from build/schedule/spec-v25-2026-08-06/QUESTIONS-FOR-BRANKO.md, the Schedule spec v23 -&gt; v25 diff. They are APPENDED as Schedule items 5-8 rather than re-ordered into the tab, so the established structure and the carried-forward wording are untouched (Rule 16); the tab note names items 5 and 6 as the decisive ones so their importance is still visible on the reader tab. TWO OF THEM EACH DECIDE A VERDICT: item 5 decides what C30041 should assert, item 6 decides whether C30012 passes or fails. Nothing was applied to TestRail - no case was edited, and the HOLDs those two items imply are PROPOSED in PROPOSED-CHANGES.md, not written.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>WHY ONE FILE AND NOT TWO (Standing Rule 55). build/branko-questions-2026-08-05/ holds a 13-item Branko sheet that is READY TO SEND and WAS NEVER SENT (register row C4). Producing a second sheet without absorbing it would leave the QA lead holding two unsent sheets for the same person - the exact 'drip of separate asks' Rule 55 exists to prevent. So this workbook CARRIES FORWARD all 13 of its items and adds 8 new ones = 21 (4 added when it was first built, and 4 more Schedule items added later the same day from the spec's move to version 25). ⚠️ ACTION NEEDED FROM THE QA LEAD: the 2026-08-05 workbook should be marked SUPERSEDED so an old one cannot go out by mistake. It was NOT edited by this pass, because this task was scoped to write only inside build/filters/questions-2026-08-06/ and build/report-suite/questions-2026-08-06/.</t>
+          <t>ONE OF THE FOUR SOURCE QUESTIONS WAS DELIBERATELY LEFT OFF, AND THIS IS THE REASON (Rule 55: ask what is unclear; it does not say invent an ask). The source file's Q2b asked what the word "labor" means in v25's new phrase "labor/status figures" - the number of HOURS or a MONEY amount. It is NOT asked, on two grounds, both checked rather than assumed. FIRST, HE HAS ALREADY ANSWERED IT IN HIS OWN WORDS: SV-8829, 2026-08-06T04:31:05-0500, verbatim "for work order lines we just show estimate and status badge, there shouldn't be totals" - which, with his 22 July no-money-on-the-Schedule ruling, says plainly that no money appears. SECOND, THE SOURCE FILE ITSELF RECORDS THAT NEITHER ANSWER CHANGES THE CASE: "Neither answer changes the case's substance; A confirms it as written." So it would have cost a PO round trip for zero test consequence - and re-asking something a source has already settled is the exact embarrassment this project has had once already. ITS ONE GENUINELY LIVE CONSEQUENCE IS ON THE SHEET as Schedule item 7: that his STORY and his SPEC now disagree (`labor/total` vs `labor/status`), which is a fork with a real answer and a named owner. The residual ambiguity is in OUR OWN text - C30011 uses "labor" for both hours and money in one expected result - and that is an internal wording repair, not a question for a product owner.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>HOW DRIFT WAS PREVENTED: every carried-forward reader-facing row is IMPORTED from the 2026-08-05 generator's own TAB1/TAB2/TAB3 lists at build time, not retyped. So the 13 carried items are byte-identical to the rows that sheet carried - the same technique the 2026-08-04 Chris consolidation used. Only the 8 new items and the tab notes are new text.</t>
+          <t>THE DESIGN-AUTHORITY QUESTION WAS DELIBERATELY *NOT* ADDED AS A NEW ROW, ON THE QA LEAD'S INSTRUCTION AND BECAUSE IT WOULD HAVE BEEN A DUPLICATE. The source file's Q4 is a two-part item. Its PRODUCT half - which drawing of the Schedule is the one to work from - is ALREADY Schedule item 4 on this very sheet, and asking it twice inside one workbook would be the drip Rule 55 exists to prevent, in miniature. Its PROCESS half - whether a design may outrank the written description in OUR OWN method - is a decision for the QA LEAD, not for Branko, and has been put to him separately. Branko is asked which drawing is canonical; he is not asked to rule on our sourcing rules.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>SV-8876 IS DELIBERATELY NOT ON THIS SHEET, AND THE BRIEF FOR THIS TASK WAS WRONG ABOUT IT. The brief listed it as "Ahtasham's clarification question, still his to answer", and CLAUDE.md's Filters section says "Branko owes SV-8876". READ LIVE FROM JIRA 2026-08-06: SV-8876 is a Task, status DONE, resolution Done, resolved 2026-08-05T08:38:16-0500, parent SV-8785, reporter Ahtasham Amjad. He CLOSED IT HIMSELF, with one comment, verbatim: "closing this as it was a gap with test case , I've updated the test case here &gt;&gt;https://shopview.testrail.io/index.php?/cases/view/29557 And created a story defect &gt;&gt; as the build is not behaving as per PRD". Putting it in front of Branko would have re-asked a closed question - the exact embarrassment this project has already had once. THE HALF THAT IS GENUINELY STILL HIS is the narrower one and IS on the sheet, as Filters item 5: did he want the buttons on one row, in which case the developer job should be cancelled? SEPARATE POINT FOR THE QA LEAD, NOT FOR BRANKO: that comment says Ahtasham EDITED OUR CASE C29557. Under Rule 38 we do not touch his cases and he should not be editing ours; this is reported, not acted on.</t>
+          <t>WHY ONE FILE AND NOT TWO (Standing Rule 55). build/branko-questions-2026-08-05/ holds a 13-item Branko sheet that is READY TO SEND and WAS NEVER SENT (register row C4). Producing a second sheet without absorbing it would leave the QA lead holding two unsent sheets for the same person - the exact 'drip of separate asks' Rule 55 exists to prevent. So this workbook CARRIES FORWARD all 13 of its items and adds 8 new ones = 21 (4 added when it was first built, and 4 more Schedule items added later the same day from the spec's move to version 25). ⚠️ ACTION NEEDED FROM THE QA LEAD: the 2026-08-05 workbook should be marked SUPERSEDED so an old one cannot go out by mistake. It was NOT edited by this pass, because this task was scoped to write only inside build/filters/questions-2026-08-06/ and build/report-suite/questions-2026-08-06/.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>THE FILTERS SPEC MOVED TO VERSION 19 THIS MORNING AND NO QUESTION WAS MANUFACTURED FROM IT. Page 572030978, version 19, 2026-08-06T11:48:47Z. Its visible change on the filter bar is S1-R3, verbatim: "Each chip displays a leading type-icon identifying the filter, the filter name, and a chevron icon indicating it opens a dropdown". THAT IS CLEAR ENOUGH TO TEST - a tester can check that each chip carries a leading icon plus a chevron, and which specific icon belongs to which chip comes from the design node the spec links. So NO ROW WAS ADDED for it (Rule 55 says ask what is unclear; it does not say invent an ask). What v19 did NOT do is resolve anything on this sheet: S9-R2 and S9-R3 are unchanged, and the S12-R2 cross-reference is still wrong. ⚠️ OWED: a proper v18 -&gt; v19 diff. This pass checked the points the sheet depends on, not the whole document, and does not claim to have diffed it.</t>
+          <t>HOW DRIFT WAS PREVENTED: every carried-forward reader-facing row is IMPORTED from the 2026-08-05 generator's own TAB1/TAB2/TAB3 lists at build time, not retyped. So the 13 carried items are byte-identical to the rows that sheet carried - the same technique the 2026-08-04 Chris consolidation used. Only the 8 new items and the tab notes are new text.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>THE SCHEDULE v23 -&gt; v25 DIFF HAS SINCE BEEN DONE, AND THIS ADDENDUM IS ITS OUTPUT - so the warning that stood here ("we have not diffed it") IS NOW OUT OF DATE and is corrected rather than deleted. Page 713031682 is at VERSION 25 (2026-08-06T09:13:51Z, re-confirmed live for this addendum); CLAUDE.md and build/OUTSTANDING-ITEMS-REGISTER.md still name version 23, and NEITHER WAS EDITED (out of scope for this pass - the record correction is owed). The diff lives at build/schedule/spec-v25-2026-08-06/SPEC-DIFF.md: 2 requirements changed, 1 governing-source change that is not a page edit, 3 cases affected. Its four reader-facing questions are Schedule items 5-8 of this sheet. Also re-confirmed by that diff and unchanged in v25: both shop-closure sentences survive, both click-menu wordings survive, and all six engineering-only topics are still absent - so items 1-3 and tab 3 stand exactly as written.</t>
+          <t>SV-8876 IS DELIBERATELY NOT ON THIS SHEET, AND THE BRIEF FOR THIS TASK WAS WRONG ABOUT IT. The brief listed it as "Ahtasham's clarification question, still his to answer", and CLAUDE.md's Filters section says "Branko owes SV-8876". READ LIVE FROM JIRA 2026-08-06: SV-8876 is a Task, status DONE, resolution Done, resolved 2026-08-05T08:38:16-0500, parent SV-8785, reporter Ahtasham Amjad. He CLOSED IT HIMSELF, with one comment, verbatim: "closing this as it was a gap with test case , I've updated the test case here &gt;&gt;https://shopview.testrail.io/index.php?/cases/view/29557 And created a story defect &gt;&gt; as the build is not behaving as per PRD". Putting it in front of Branko would have re-asked a closed question - the exact embarrassment this project has already had once. THE HALF THAT IS GENUINELY STILL HIS is the narrower one and IS on the sheet, as Filters item 5: did he want the buttons on one row, in which case the developer job should be cancelled? SEPARATE POINT FOR THE QA LEAD, NOT FOR BRANKO: that comment says Ahtasham EDITED OUR CASE C29557. Under Rule 38 we do not touch his cases and he should not be editing ours; this is reported, not acted on.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>WORDING RULES APPLIED (Standing Rules 7 and 55): every reader-facing question row names the PROJECT (Filters or Schedule) and the SCREEN, because Branko owns THREE projects - Filters, Schedule and Global Search - so a row read on its own, days later, on a phone must still be unambiguous. Story and epic keys appear in plain form only where they orient him. No case IDs, no requirement anchors, no technical terms and not the word VIU appear anywhere he reads. Each question is a plain A/B/C with a blank for the answer, and each carries a one-line reason so the consequence is visible.</t>
+          <t>THE FILTERS SPEC MOVED TO VERSION 19 THIS MORNING AND NO QUESTION WAS MANUFACTURED FROM IT. Page 572030978, version 19, 2026-08-06T11:48:47Z. Its visible change on the filter bar is S1-R3, verbatim: "Each chip displays a leading type-icon identifying the filter, the filter name, and a chevron icon indicating it opens a dropdown". THAT IS CLEAR ENOUGH TO TEST - a tester can check that each chip carries a leading icon plus a chevron, and which specific icon belongs to which chip comes from the design node the spec links. So NO ROW WAS ADDED for it (Rule 55 says ask what is unclear; it does not say invent an ask). What v19 did NOT do is resolve anything on this sheet: S9-R2 and S9-R3 are unchanged, and the S12-R2 cross-reference is still wrong. ⚠️ OWED: a proper v18 -&gt; v19 diff. This pass checked the points the sheet depends on, not the whole document, and does not claim to have diffed it.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>SOURCE-CURRENCY (Standing Rules 31 and 59), fetched LIVE and re-read immediately before writing, 2026-08-06: Filters spec page 572030978 = VERSION 19, HTTP 200 (in-body field still reads "Version: 1.6" - the Rule-31(a) trap; the CONFLUENCE number is the one used). Schedule spec page 713031682 = VERSION 25, HTTP 200, and STALE against our records at 23. Jira read live for SV-8876, SV-8825, SV-8915, SV-8916, SV-8917. TestRail read live for all 114 Filters cases. Designs = PARTIAL, and which artefact is canonical is Schedule item 4 on this very sheet. ADDENDUM, 2026-08-06: for the four new Schedule items the Schedule spec was RE-FETCHED live (page 713031682, version 25, HTTP 200, by Branko Cicovic at 09:13:51Z) and every sentence they rest on was searched in its body; JIRA was read live and read-only for SV-8686, SV-8695, SV-8829, SV-8874, SV-8837 and SV-8915; and FOUR SCHEDULE CASES WERE PULLED LIVE FROM TESTRAIL - C30041, C30012, C30011 and C30001, all HTTP 200, titles, refs and automation markers read from the live cases rather than from our records. So the earlier line saying "Schedule cases were NOT re-pulled this pass" now holds only for the THREE HELD C-ids on items 1-3 (C29983, C30089, C43555), which still come from committed records and are still cited as such.</t>
+          <t>THE SCHEDULE v23 -&gt; v25 DIFF HAS SINCE BEEN DONE, AND THIS ADDENDUM IS ITS OUTPUT - so the warning that stood here ("we have not diffed it") IS NOW OUT OF DATE and is corrected rather than deleted. Page 713031682 is at VERSION 25 (2026-08-06T09:13:51Z, re-confirmed live for this addendum); CLAUDE.md and build/OUTSTANDING-ITEMS-REGISTER.md still name version 23, and NEITHER WAS EDITED (out of scope for this pass - the record correction is owed). The diff lives at build/schedule/spec-v25-2026-08-06/SPEC-DIFF.md: 2 requirements changed, 1 governing-source change that is not a page edit, 3 cases affected. Its four reader-facing questions are Schedule items 5-8 of this sheet. Also re-confirmed by that diff and unchanged in v25: both shop-closure sentences survive, both click-menu wordings survive, and all six engineering-only topics are still absent - so items 1-3 and tab 3 stand exactly as written.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>THE BUILD WAS NOT OBSERVED (Standing Rules 12, 49, 60). The shared QA sign-in is dead - a read-only probe returned HTTP 401 {"error":"sso_required"} - and quick-login and switch-user were deliberately NOT called, because both rotate the shared session and would sign concurrent workers out of the other branches. BOTH BRANCHES HAVE ALSO REDEPLOYED: sv8785.qa.shopview.com now reads app-version v3.4.2-280ca5a (last-modified Thu 06 Aug 2026 09:37:49 GMT) where the Filters passes ran on v3.4.2-d00239b. So every build-side sentence quoted to Branko - the Status chip behaving as the description says, the filter bar on one row, the capital F - comes from a build that no longer exists, and is worded to him as what the product does rather than as a fresh measurement. All Filters and Schedule verdicts remain PROVISIONAL and the Rule-49 queues are OPEN.</t>
+          <t>WORDING RULES APPLIED (Standing Rules 7 and 55): every reader-facing question row names the PROJECT (Filters or Schedule) and the SCREEN, because Branko owns THREE projects - Filters, Schedule and Global Search - so a row read on its own, days later, on a phone must still be unambiguous. Story and epic keys appear in plain form only where they orient him. No case IDs, no requirement anchors, no technical terms and not the word VIU appear anywhere he reads. Each question is a plain A/B/C with a blank for the answer, and each carries a one-line reason so the consequence is visible.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE-CURRENCY (Standing Rules 31 and 59), fetched LIVE and re-read immediately before writing, 2026-08-06: Filters spec page 572030978 = VERSION 19, HTTP 200 (in-body field still reads "Version: 1.6" - the Rule-31(a) trap; the CONFLUENCE number is the one used). Schedule spec page 713031682 = VERSION 25, HTTP 200, and STALE against our records at 23. Jira read live for SV-8876, SV-8825, SV-8915, SV-8916, SV-8917. TestRail read live for all 114 Filters cases. Designs = PARTIAL, and which artefact is canonical is Schedule item 4 on this very sheet. ADDENDUM, 2026-08-06: for the four new Schedule items the Schedule spec was RE-FETCHED live (page 713031682, version 25, HTTP 200, by Branko Cicovic at 09:13:51Z) and every sentence they rest on was searched in its body; JIRA was read live and read-only for SV-8686, SV-8695, SV-8829, SV-8874, SV-8837 and SV-8915; and FOUR SCHEDULE CASES WERE PULLED LIVE FROM TESTRAIL - C30041, C30012, C30011 and C30001, all HTTP 200, titles, refs and automation markers read from the live cases rather than from our records. So the earlier line saying "Schedule cases were NOT re-pulled this pass" now holds only for the THREE HELD C-ids on items 1-3 (C29983, C30089, C43555), which still come from committed records and are still cited as such.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>THE BUILD WAS NOT OBSERVED (Standing Rules 12, 49, 60). The shared QA sign-in is dead - a read-only probe returned HTTP 401 {"error":"sso_required"} - and quick-login and switch-user were deliberately NOT called, because both rotate the shared session and would sign concurrent workers out of the other branches. BOTH BRANCHES HAVE ALSO REDEPLOYED: sv8785.qa.shopview.com now reads app-version v3.4.2-280ca5a (last-modified Thu 06 Aug 2026 09:37:49 GMT) where the Filters passes ran on v3.4.2-d00239b. So every build-side sentence quoted to Branko - the Status chip behaving as the description says, the filter bar on one row, the capital F - comes from a build that no longer exists, and is worded to him as what the product does rather than as a fresh measurement. All Filters and Schedule verdicts remain PROVISIONAL and the Rule-49 queues are OPEN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>NOTHING HAS BEEN WRITTEN ANYWHERE. This sheet is a draft for the QA lead to send. Read-only on TestRail (get_sections, get_cases), on Confluence (GET content) and on Jira (GET issue). No TestRail write, no Jira write, no case edit, no run write, no application call. CLAUDE.md, build/OUTSTANDING-ITEMS-REGISTER.md and build/APP-ACTIONS-PLAYBOOK.md were not touched, and neither was the 2026-08-05 Branko workbook.</t>
         </is>
